--- a/outputs/daily/hr_rankings_2026-10-27.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-27.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -768,11 +768,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>57.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -786,65 +798,61 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>37.8</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -881,7 +889,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -954,14 +962,46 @@
           <t>0.2549</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1000,12 +1040,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1024,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>54.3</v>
+        <v>57.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1038,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1048,10 +1088,10 @@
         <v>40.1</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1061,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1236,8 +1272,16 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1251,24 +1295,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -1276,22 +1320,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1300,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.4</v>
+        <v>55.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1314,62 +1358,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>50.1</v>
+        <v>48.9</v>
       </c>
       <c r="Q4" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="R4" t="n">
         <v>40.1</v>
       </c>
-      <c r="R4" t="n">
-        <v>27.6</v>
-      </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>63.3</v>
+        <v>28.9</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1389,12 +1429,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1404,12 +1444,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1419,101 +1459,109 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1527,24 +1575,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -1552,19 +1600,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>50.4</v>
+        <v>52.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1578,65 +1638,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>28.9</v>
+        <v>63.3</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1653,12 +1709,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1668,12 +1724,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1683,77 +1739,109 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>0.1951</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1792,12 +1880,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1816,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49.7</v>
+        <v>50.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1830,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1840,10 +1928,10 @@
         <v>40.1</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -1853,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2028,8 +2112,16 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2043,12 +2135,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2068,12 +2160,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2092,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.6</v>
+        <v>50.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2106,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>47.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
         <v>40.1</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>13.3</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2181,7 +2269,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -2191,12 +2279,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2206,72 +2294,72 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2304,8 +2392,16 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2319,12 +2415,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2344,19 +2440,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>46.6</v>
+        <v>49.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2370,65 +2478,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.6</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>54.9</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2445,27 +2549,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2475,77 +2579,109 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>32.39</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>0.1617</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2559,24 +2695,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -2584,19 +2720,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>46.4</v>
+        <v>48.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2610,65 +2758,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>20.9</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2685,27 +2829,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2715,77 +2859,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2799,12 +2975,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2824,12 +3000,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2848,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2862,62 +3038,58 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>47.1</v>
       </c>
       <c r="Q10" t="n">
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>13.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2937,7 +3109,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2947,87 +3119,87 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3060,8 +3232,16 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3075,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -3100,22 +3280,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3138,62 +3318,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>43.4</v>
       </c>
       <c r="Q11" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="R11" t="n">
         <v>40.1</v>
       </c>
-      <c r="R11" t="n">
-        <v>27.6</v>
-      </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3213,27 +3389,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3243,101 +3419,109 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3376,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3384,11 +3568,23 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>35.6</v>
+        <v>41.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3402,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
         <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
         <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3497,7 +3689,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3570,14 +3762,46 @@
           <t>0.1347</t>
         </is>
       </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3616,19 +3840,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>40.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3642,65 +3878,61 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
         <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3737,7 +3969,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3810,14 +4042,46 @@
           <t>0.151</t>
         </is>
       </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3831,24 +4095,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -3856,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3866,12 +4130,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -3880,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.6</v>
+        <v>37.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3894,65 +4158,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>16.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>38.7</v>
+        <v>46.2</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>5.1</v>
+        <v>19.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -3969,12 +4229,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -3984,12 +4244,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -3999,101 +4259,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4107,24 +4375,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -4132,19 +4400,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>32.2</v>
+        <v>36.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4158,65 +4438,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4233,12 +4509,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4248,12 +4524,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4263,77 +4539,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>0.0974</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4372,19 +4680,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>31.8</v>
+        <v>35.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4398,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
         <v>0.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
         <v>15.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4493,7 +4809,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4566,14 +4882,46 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4612,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4636,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.4</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4650,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -4660,10 +5008,10 @@
         <v>40.1</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -4673,39 +5021,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4848,8 +5192,16 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4888,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -4912,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.3</v>
+        <v>33.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4926,7 +5278,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -4936,10 +5288,10 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
@@ -4949,39 +5301,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5124,8 +5472,16 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5164,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5172,11 +5528,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>32.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5190,20 +5558,20 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>44.4</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5213,42 +5581,38 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5285,7 +5649,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5358,14 +5722,46 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5730,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5738,11 +6134,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>57.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5756,65 +6164,61 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>37.8</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -5851,7 +6255,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -5924,14 +6328,46 @@
           <t>0.2549</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5970,12 +6406,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -5994,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>54.3</v>
+        <v>57.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6008,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6018,10 +6454,10 @@
         <v>40.1</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6031,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6206,8 +6638,16 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6221,24 +6661,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -6246,22 +6686,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -6270,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.4</v>
+        <v>55.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6284,62 +6724,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>50.1</v>
+        <v>48.9</v>
       </c>
       <c r="Q4" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="R4" t="n">
         <v>40.1</v>
       </c>
-      <c r="R4" t="n">
-        <v>27.6</v>
-      </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>63.3</v>
+        <v>28.9</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6359,12 +6795,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -6374,12 +6810,12 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -6389,101 +6825,109 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6497,24 +6941,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -6522,19 +6966,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>50.4</v>
+        <v>52.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6548,65 +7004,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>28.9</v>
+        <v>63.3</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -6623,12 +7075,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -6638,12 +7090,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -6653,77 +7105,109 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>0.1951</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6762,12 +7246,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -6786,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49.7</v>
+        <v>50.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6800,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -6810,10 +7294,10 @@
         <v>40.1</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -6823,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6998,8 +7478,16 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7013,12 +7501,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7038,12 +7526,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7062,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.6</v>
+        <v>50.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7076,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>47.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
         <v>40.1</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>13.3</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7151,7 +7635,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -7161,12 +7645,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -7176,72 +7660,72 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -7274,8 +7758,16 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7289,12 +7781,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7314,19 +7806,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>46.6</v>
+        <v>49.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7340,65 +7844,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.6</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>54.9</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -7415,27 +7915,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -7445,77 +7945,109 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>32.39</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>0.1617</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7529,24 +8061,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -7554,19 +8086,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>46.4</v>
+        <v>48.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -7580,65 +8124,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>20.9</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -7655,27 +8195,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -7685,77 +8225,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7769,12 +8341,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -7794,12 +8366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -7818,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -7832,62 +8404,58 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>47.1</v>
       </c>
       <c r="Q10" t="n">
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>13.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7907,7 +8475,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -7917,87 +8485,87 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -8030,8 +8598,16 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8045,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -8070,22 +8646,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -8108,62 +8684,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>43.4</v>
       </c>
       <c r="Q11" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="R11" t="n">
         <v>40.1</v>
       </c>
-      <c r="R11" t="n">
-        <v>27.6</v>
-      </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8183,27 +8755,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8213,101 +8785,109 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>58.98</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8346,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8354,11 +8934,23 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>35.6</v>
+        <v>41.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8372,65 +8964,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
         <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
         <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8467,7 +9055,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8540,14 +9128,46 @@
           <t>0.1347</t>
         </is>
       </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8586,19 +9206,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>40.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8612,65 +9244,61 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
         <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
         <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -8707,7 +9335,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -8780,14 +9408,46 @@
           <t>0.151</t>
         </is>
       </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8801,24 +9461,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -8826,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -8836,12 +9496,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -8850,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.6</v>
+        <v>37.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8864,65 +9524,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>16.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>38.7</v>
+        <v>46.2</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>5.1</v>
+        <v>19.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -8939,12 +9595,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -8954,12 +9610,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -8969,101 +9625,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9077,24 +9741,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-28T00:00:00Z</t>
@@ -9102,19 +9766,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>32.2</v>
+        <v>36.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9128,65 +9804,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9203,12 +9875,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9218,12 +9890,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9233,77 +9905,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>0.0974</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9342,19 +10046,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>31.8</v>
+        <v>35.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9368,65 +10084,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
         <v>0.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>46.2</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
         <v>15.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -9463,7 +10175,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -9536,14 +10248,46 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9582,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -9606,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.4</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9620,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -9630,10 +10374,10 @@
         <v>40.1</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -9643,39 +10387,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9818,8 +10558,16 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9858,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -9882,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.3</v>
+        <v>33.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -9896,7 +10644,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -9906,10 +10654,10 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
@@ -9919,39 +10667,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -10094,8 +10838,16 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10134,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10142,11 +10894,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Dustin May</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>669160</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>32.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10160,20 +10924,20 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>44.4</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10183,42 +10947,38 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -10255,7 +11015,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10328,14 +11088,46 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>90.18</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.1595</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
